--- a/datasets/tenant-inputs/generated/meridian-health/standard-2026-07-v3/core-dimensions/15_industry_context_patterns.xlsx
+++ b/datasets/tenant-inputs/generated/meridian-health/standard-2026-07-v3/core-dimensions/15_industry_context_patterns.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R4de850b09e3d4a70"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R29734627bda84f40"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R6a879c8976584423"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R457a7eb349a440c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R8f89d19807b94a18"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="R6646ac2557b243a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R751e24d9a4004a1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R9d2751e45e9041b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R84da028e0c204c37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="Rbaad17d37ce140c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R8de319312db84cac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="R6353fc62581a4185"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -618,7 +618,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf828aab7ce424809"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15d2d775cdef4ab0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -749,7 +749,7 @@
         <x:v>AbarVa synthetic industry pattern library</x:v>
       </x:c>
       <x:c r="J6" s="78" t="str">
-        <x:v>Validate with client-specific operating model and evidence.</x:v>
+        <x:v>Validate selected record (record 1) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for industry context patterns.</x:v>
       </x:c>
       <x:c r="K6" s="41" t="str">
         <x:v>Medium</x:v>
@@ -784,7 +784,7 @@
         <x:v>AbarVa synthetic industry pattern library</x:v>
       </x:c>
       <x:c r="J7" s="79" t="str">
-        <x:v>Validate with client-specific operating model and evidence.</x:v>
+        <x:v>Confirm selected record (record 2) current-vs-target status, module boundary, volume baseline, and relationship links before this industry context patterns record is used downstream.</x:v>
       </x:c>
       <x:c r="K7" s="45" t="str">
         <x:v>High</x:v>
@@ -819,7 +819,7 @@
         <x:v>AbarVa synthetic industry pattern library</x:v>
       </x:c>
       <x:c r="J8" t="str">
-        <x:v>Validate with client-specific operating model and evidence.</x:v>
+        <x:v>Attach client evidence for selected record (record 3), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="K8" t="str">
         <x:v>High</x:v>
@@ -854,7 +854,7 @@
         <x:v>AbarVa synthetic industry pattern library</x:v>
       </x:c>
       <x:c r="J9" t="str">
-        <x:v>Validate with client-specific operating model and evidence.</x:v>
+        <x:v>Reconcile selected record (record 4) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="K9" t="str">
         <x:v>High</x:v>
@@ -889,7 +889,7 @@
         <x:v>AbarVa synthetic industry pattern library</x:v>
       </x:c>
       <x:c r="J10" t="str">
-        <x:v>Validate with client-specific operating model and evidence.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for selected record (record 5) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="K10" t="str">
         <x:v>High</x:v>
@@ -924,7 +924,7 @@
         <x:v>AbarVa synthetic industry pattern library</x:v>
       </x:c>
       <x:c r="J11" t="str">
-        <x:v>Validate with client-specific operating model and evidence.</x:v>
+        <x:v>Validate selected record (record 6) against Agent Assist / Member Service evidence: stale knowledge article duplicates; confirm human-approved next-best-action workflow owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="K11" t="str">
         <x:v>Medium</x:v>
@@ -959,7 +959,7 @@
         <x:v>AbarVa synthetic industry pattern library</x:v>
       </x:c>
       <x:c r="J12" t="str">
-        <x:v>Validate with client-specific operating model and evidence.</x:v>
+        <x:v>Confirm selected record (record 7) current-vs-target status, module boundary, volume baseline, and relationship links before this industry context patterns record is used downstream.</x:v>
       </x:c>
       <x:c r="K12" t="str">
         <x:v>High</x:v>
@@ -994,7 +994,7 @@
         <x:v>AbarVa synthetic industry pattern library</x:v>
       </x:c>
       <x:c r="J13" t="str">
-        <x:v>Validate with client-specific operating model and evidence.</x:v>
+        <x:v>Validate selected record (record 8) against Finance Analytics evidence: slow close-window dashboards; confirm vendor master harmonization owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="K13" t="str">
         <x:v>High</x:v>
@@ -1029,7 +1029,7 @@
         <x:v>AbarVa synthetic industry pattern library</x:v>
       </x:c>
       <x:c r="J14" t="str">
-        <x:v>Validate with client-specific operating model and evidence.</x:v>
+        <x:v>Reconcile selected record (record 9) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="K14" t="str">
         <x:v>High</x:v>
@@ -1064,7 +1064,7 @@
         <x:v>AbarVa synthetic industry pattern library</x:v>
       </x:c>
       <x:c r="J15" t="str">
-        <x:v>Validate with client-specific operating model and evidence.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for selected record (record 10) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="K15" t="str">
         <x:v>High</x:v>
@@ -1099,7 +1099,7 @@
         <x:v>AbarVa synthetic industry pattern library</x:v>
       </x:c>
       <x:c r="J16" t="str">
-        <x:v>Validate with client-specific operating model and evidence.</x:v>
+        <x:v>Validate selected record (record 11) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for industry context patterns.</x:v>
       </x:c>
       <x:c r="K16" t="str">
         <x:v>Medium</x:v>
@@ -1134,7 +1134,7 @@
         <x:v>AbarVa synthetic industry pattern library</x:v>
       </x:c>
       <x:c r="J17" t="str">
-        <x:v>Validate with client-specific operating model and evidence.</x:v>
+        <x:v>Confirm selected record (record 12) current-vs-target status, module boundary, volume baseline, and relationship links before this industry context patterns record is used downstream.</x:v>
       </x:c>
       <x:c r="K17" t="str">
         <x:v>High</x:v>
@@ -1169,7 +1169,7 @@
         <x:v>AbarVa synthetic industry pattern library</x:v>
       </x:c>
       <x:c r="J18" t="str">
-        <x:v>Validate with client-specific operating model and evidence.</x:v>
+        <x:v>Attach client evidence for selected record (record 13), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="K18" t="str">
         <x:v>High</x:v>
@@ -1204,7 +1204,7 @@
         <x:v>AbarVa synthetic industry pattern library</x:v>
       </x:c>
       <x:c r="J19" t="str">
-        <x:v>Validate with client-specific operating model and evidence.</x:v>
+        <x:v>Reconcile selected record (record 14) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="K19" t="str">
         <x:v>High</x:v>
@@ -1239,7 +1239,7 @@
         <x:v>AbarVa synthetic industry pattern library</x:v>
       </x:c>
       <x:c r="J20" t="str">
-        <x:v>Validate with client-specific operating model and evidence.</x:v>
+        <x:v>Validate selected record (record 15) against Agent Assist / Member Service evidence: stale knowledge article duplicates; confirm human-approved next-best-action workflow owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="K20" t="str">
         <x:v>High</x:v>
@@ -1274,7 +1274,7 @@
         <x:v>AbarVa synthetic industry pattern library</x:v>
       </x:c>
       <x:c r="J21" t="str">
-        <x:v>Validate with client-specific operating model and evidence.</x:v>
+        <x:v>Validate selected record (record 16) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for industry context patterns.</x:v>
       </x:c>
       <x:c r="K21" t="str">
         <x:v>Medium</x:v>
@@ -1309,7 +1309,7 @@
         <x:v>AbarVa synthetic industry pattern library</x:v>
       </x:c>
       <x:c r="J22" t="str">
-        <x:v>Validate with client-specific operating model and evidence.</x:v>
+        <x:v>Confirm selected record (record 17) current-vs-target status, module boundary, volume baseline, and relationship links before this industry context patterns record is used downstream.</x:v>
       </x:c>
       <x:c r="K22" t="str">
         <x:v>High</x:v>
@@ -1344,7 +1344,7 @@
         <x:v>AbarVa synthetic industry pattern library</x:v>
       </x:c>
       <x:c r="J23" t="str">
-        <x:v>Validate with client-specific operating model and evidence.</x:v>
+        <x:v>Attach client evidence for selected record (record 18), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="K23" t="str">
         <x:v>High</x:v>
@@ -1379,7 +1379,7 @@
         <x:v>AbarVa synthetic industry pattern library</x:v>
       </x:c>
       <x:c r="J24" t="str">
-        <x:v>Validate with client-specific operating model and evidence.</x:v>
+        <x:v>Reconcile selected record (record 19) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="K24" t="str">
         <x:v>High</x:v>
@@ -1414,7 +1414,7 @@
         <x:v>AbarVa synthetic industry pattern library</x:v>
       </x:c>
       <x:c r="J25" t="str">
-        <x:v>Validate with client-specific operating model and evidence.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for selected record (record 20) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="K25" t="str">
         <x:v>High</x:v>
@@ -1438,7 +1438,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6731b52670084e27"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb129f8b84da409c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1513,7 +1513,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07bad799834f4d81"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R677ff2784fd14357"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1657,7 +1657,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43833605e6f94836"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R90142f48060c4129"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1727,7 +1727,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b72da6664924007"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd56ab09e986a4633"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1837,7 +1837,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8cc4134748a14530"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc93a8943753347da"/>
   </x:tableParts>
 </x:worksheet>
 </file>